--- a/misc/player_group_pca_results.xlsx
+++ b/misc/player_group_pca_results.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Goals_Report" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="home_Goalkeeper_loadings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="home_Goalkeeper_variance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="away_Goalkeeper_loadings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="away_Goalkeeper_variance" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="home_Defenders_loadings" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="home_Defenders_variance" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="away_Defenders_loadings" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="away_Defenders_variance" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="home_Midfielders_loadings" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="home_Midfielders_variance" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="away_Midfielders_loadings" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="away_Midfielders_variance" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="home_Attackers_loadings" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="home_Attackers_variance" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="away_Attackers_loadings" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="away_Attackers_variance" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Goals_Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="home_Goalkeeper_loadings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="home_Goalkeeper_variance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="away_Goalkeeper_loadings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="away_Goalkeeper_variance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="home_Defenders_loadings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="home_Defenders_variance" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="away_Defenders_loadings" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="away_Defenders_variance" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="home_Midfielders_loadings" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="home_Midfielders_variance" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="away_Midfielders_loadings" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="away_Midfielders_variance" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="home_Attackers_loadings" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="home_Attackers_variance" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="away_Attackers_loadings" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="away_Attackers_variance" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6166614620539317</v>
+        <v>0.6166614620539318</v>
       </c>
       <c r="E2" t="n">
-        <v>61.66614620539317</v>
+        <v>61.66614620539318</v>
       </c>
       <c r="F2" t="n">
-        <v>78.11225148226572</v>
+        <v>78.11225148226576</v>
       </c>
     </row>
     <row r="3">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6152841912169235</v>
+        <v>0.6152841912169233</v>
       </c>
       <c r="E3" t="n">
         <v>61.52841912169234</v>
       </c>
       <c r="F3" t="n">
-        <v>78.10143921972545</v>
+        <v>78.10143921972544</v>
       </c>
     </row>
     <row r="4">
@@ -540,13 +540,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.503018590360603</v>
+        <v>0.5030185903606031</v>
       </c>
       <c r="E4" t="n">
         <v>50.30185903606031</v>
       </c>
       <c r="F4" t="n">
-        <v>70.80006638582563</v>
+        <v>70.80006638582564</v>
       </c>
     </row>
     <row r="5">
@@ -570,7 +570,7 @@
         <v>49.38013583771318</v>
       </c>
       <c r="F5" t="n">
-        <v>70.19986563408304</v>
+        <v>70.19986563408303</v>
       </c>
     </row>
     <row r="6">
@@ -594,7 +594,7 @@
         <v>46.7751514527445</v>
       </c>
       <c r="F6" t="n">
-        <v>67.31524246635229</v>
+        <v>67.31524246635226</v>
       </c>
     </row>
     <row r="7">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.474019129159479</v>
+        <v>0.4740191291594792</v>
       </c>
       <c r="E7" t="n">
-        <v>47.4019129159479</v>
+        <v>47.40191291594792</v>
       </c>
       <c r="F7" t="n">
-        <v>67.67596691658382</v>
+        <v>67.67596691658383</v>
       </c>
     </row>
     <row r="8">
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4824013165743099</v>
+        <v>0.4824013165743098</v>
       </c>
       <c r="E8" t="n">
-        <v>48.24013165743099</v>
+        <v>48.24013165743098</v>
       </c>
       <c r="F8" t="n">
-        <v>66.10915826955203</v>
+        <v>66.109158269552</v>
       </c>
     </row>
     <row r="9">
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4794226640017988</v>
+        <v>0.4794226640017987</v>
       </c>
       <c r="E9" t="n">
         <v>47.94226640017988</v>
       </c>
       <c r="F9" t="n">
-        <v>66.24551044958604</v>
+        <v>66.24551044958602</v>
       </c>
     </row>
   </sheetData>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2081972979636986</v>
+        <v>0.2081972979636985</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7019986563408304</v>
+        <v>0.7019986563408303</v>
       </c>
     </row>
     <row r="4">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1051497246625392</v>
+        <v>0.1051497246625391</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8071483810033695</v>
+        <v>0.8071483810033694</v>
       </c>
     </row>
     <row r="5">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07711061892283097</v>
+        <v>0.07711061892283083</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8842589999262005</v>
+        <v>0.8842589999262003</v>
       </c>
     </row>
     <row r="6">
@@ -757,7 +757,7 @@
         <v>0.05705525474733938</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9413142546735399</v>
+        <v>0.9413142546735397</v>
       </c>
     </row>
     <row r="7">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02608161185976388</v>
+        <v>0.02608161185976395</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9673958665333038</v>
+        <v>0.9673958665333037</v>
       </c>
     </row>
     <row r="8">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02155226679953884</v>
+        <v>0.02155226679953894</v>
       </c>
       <c r="C8" t="n">
         <v>0.9889481333328426</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01105186666715752</v>
+        <v>0.01105186666715761</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -865,25 +865,25 @@
         <v>0.2429786711493759</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0437697970467065</v>
+        <v>-0.04376979704670667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5643715672817388</v>
+        <v>0.5643715672817403</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7502418027687899</v>
+        <v>0.7502418027687878</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2293874324970009</v>
+        <v>0.229387432497002</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.01735647858776805</v>
+        <v>-0.01735647858776831</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0246020143241056</v>
+        <v>-0.02460201432410327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06436179775166517</v>
+        <v>0.06436179775166539</v>
       </c>
     </row>
     <row r="3">
@@ -893,28 +893,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4788254889606038</v>
+        <v>0.478825488960604</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09887606814611366</v>
+        <v>0.09887606814611381</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06209045782259909</v>
+        <v>-0.06209045782259927</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03700962497425762</v>
+        <v>-0.03700962497425799</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1535175060831027</v>
+        <v>-0.1535175060831022</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5174808657640455</v>
+        <v>-0.5174808657640391</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6741789348366661</v>
+        <v>0.6741789348366688</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09926444324563194</v>
+        <v>-0.09926444324564719</v>
       </c>
     </row>
     <row r="4">
@@ -927,25 +927,25 @@
         <v>0.1063173645997851</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4405987205784204</v>
+        <v>-0.4405987205784206</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6520918634512256</v>
+        <v>0.6520918634512242</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5166734291773053</v>
+        <v>-0.5166734291773063</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1470577688177226</v>
+        <v>-0.1470577688177221</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1393687418383036</v>
+        <v>0.1393687418383062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1257115917807132</v>
+        <v>0.1257115917807182</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2134036474215205</v>
+        <v>0.2134036474215167</v>
       </c>
     </row>
     <row r="5">
@@ -955,28 +955,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4067910323318744</v>
+        <v>0.4067910323318745</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2297762885313576</v>
+        <v>-0.2297762885313566</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2874802323458632</v>
+        <v>-0.2874802323458641</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07399326462640192</v>
+        <v>-0.0739932646264016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5683773983958248</v>
+        <v>0.5683773983958246</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5473320481614273</v>
+        <v>0.547332048161429</v>
       </c>
       <c r="H5" t="n">
-        <v>0.250382013150082</v>
+        <v>0.250382013150073</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09103645194393979</v>
+        <v>-0.09103645194395157</v>
       </c>
     </row>
     <row r="6">
@@ -986,28 +986,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4682508947959587</v>
+        <v>0.4682508947959585</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.07736726849245271</v>
+        <v>-0.0773672684924526</v>
       </c>
       <c r="D6" t="n">
         <v>-0.2960412782221162</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04936634913071825</v>
+        <v>0.04936634913071952</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.189355583717958</v>
+        <v>-0.1893555837179568</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.06083324247262172</v>
+        <v>-0.0608332424726209</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3276126890900917</v>
+        <v>-0.3276126890900703</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7333427820079625</v>
+        <v>0.7333427820079724</v>
       </c>
     </row>
     <row r="7">
@@ -1017,28 +1017,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4511627909250792</v>
+        <v>0.4511627909250794</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2890091530456652</v>
+        <v>-0.2890091530456651</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02960786354559745</v>
+        <v>-0.02960786354559699</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02664928760665788</v>
+        <v>-0.02664928760665758</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2575631371034123</v>
+        <v>-0.2575631371034145</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.08452851464277698</v>
+        <v>-0.08452851464278564</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4977302973910954</v>
+        <v>-0.497730297391112</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6245956668946319</v>
+        <v>-0.6245956668946164</v>
       </c>
     </row>
     <row r="8">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2433598759791732</v>
+        <v>0.2433598759791729</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6016547148059938</v>
+        <v>0.6016547148059933</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1496016613072457</v>
+        <v>0.1496016613072463</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00571554887417317</v>
+        <v>0.005715548874173607</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4587437862870004</v>
+        <v>-0.4587437862870006</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5785946337076199</v>
+        <v>0.5785946337076207</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0830531709798886</v>
+        <v>0.08305317097988155</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06525955507277474</v>
+        <v>-0.06525955507277892</v>
       </c>
     </row>
     <row r="9">
@@ -1079,28 +1079,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.229944334259238</v>
+        <v>0.2299443342592379</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5384078120174627</v>
+        <v>0.5384078120174628</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2426171998465965</v>
+        <v>0.242617199846596</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4002014504649139</v>
+        <v>-0.400201450464915</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5162313034144216</v>
+        <v>0.5162313034144204</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2594200950972199</v>
+        <v>-0.2594200950972227</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3231402105787554</v>
+        <v>-0.3231402105787534</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002276933669343059</v>
+        <v>0.002276933669352141</v>
       </c>
     </row>
   </sheetData>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2054009101360779</v>
+        <v>0.2054009101360776</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6731524246635229</v>
+        <v>0.6731524246635225</v>
       </c>
     </row>
     <row r="4">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1193811995558544</v>
+        <v>0.1193811995558545</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7925336242193772</v>
+        <v>0.792533624219377</v>
       </c>
     </row>
     <row r="5">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09957145918519861</v>
+        <v>0.09957145918519862</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8921050834045758</v>
+        <v>0.8921050834045756</v>
       </c>
     </row>
     <row r="6">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05419245897639514</v>
+        <v>0.05419245897639517</v>
       </c>
       <c r="C6" t="n">
-        <v>0.946297542380971</v>
+        <v>0.9462975423809707</v>
       </c>
     </row>
     <row r="7">
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02601220142988826</v>
+        <v>0.02601220142988822</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9723097438108592</v>
+        <v>0.972309743810859</v>
       </c>
     </row>
     <row r="8">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01492440009515626</v>
+        <v>0.01492440009515624</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9872341439060155</v>
+        <v>0.9872341439060153</v>
       </c>
     </row>
     <row r="9">
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01276585609398459</v>
+        <v>0.01276585609398466</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1299,25 +1299,25 @@
         <v>0.254741375311103</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.04909298289015408</v>
+        <v>-0.04909298289015399</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5010738319333675</v>
+        <v>0.5010738319333691</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7966044693369017</v>
+        <v>0.7966044693369</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2076666963321882</v>
+        <v>0.2076666963321885</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02093851771998991</v>
+        <v>-0.02093851771998926</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02269355827125361</v>
+        <v>-0.02269355827125339</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05444418465542309</v>
+        <v>0.05444418465542333</v>
       </c>
     </row>
     <row r="3">
@@ -1327,28 +1327,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.476702710689895</v>
+        <v>0.4767027106898949</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09656425194053285</v>
+        <v>0.09656425194053249</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04899976366892984</v>
+        <v>-0.04899976366892958</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05571444933789815</v>
+        <v>-0.05571444933789803</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1751499922130962</v>
+        <v>-0.1751499922130951</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4863951755278207</v>
+        <v>-0.4863951755278217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6921439667061777</v>
+        <v>0.6921439667061769</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1077206431780191</v>
+        <v>-0.1077206431780215</v>
       </c>
     </row>
     <row r="4">
@@ -1358,28 +1358,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1120140631356011</v>
+        <v>0.1120140631356012</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.440698639276933</v>
+        <v>-0.4406986392769307</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6842130561317763</v>
+        <v>0.684213056131775</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4804875286750441</v>
+        <v>-0.4804875286750453</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.07888442988454004</v>
+        <v>-0.07888442988453988</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1565308113938319</v>
+        <v>0.156530811393832</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1187268873807632</v>
+        <v>0.118726887380764</v>
       </c>
       <c r="I4" t="n">
-        <v>0.222263504932622</v>
+        <v>0.2222635049326224</v>
       </c>
     </row>
     <row r="5">
@@ -1389,28 +1389,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3983201771355345</v>
+        <v>0.3983201771355346</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2385173846807814</v>
+        <v>-0.2385173846807816</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3248623486692592</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.05437244961548225</v>
+        <v>-0.0543724496154817</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5563859955456552</v>
+        <v>0.5563859955456526</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5457638755531337</v>
+        <v>0.5457638755531353</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2394033212831078</v>
+        <v>0.2394033212831083</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1059294609264717</v>
+        <v>-0.1059294609264726</v>
       </c>
     </row>
     <row r="6">
@@ -1420,28 +1420,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4636108439846861</v>
+        <v>0.4636108439846858</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.08458179305162435</v>
+        <v>-0.08458179305162494</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3025618001124504</v>
+        <v>-0.3025618001124505</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0259154769520807</v>
+        <v>0.0259154769520813</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1933268303335607</v>
+        <v>-0.1933268303335598</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.07497843476901342</v>
+        <v>-0.07497843476901471</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3136246147892667</v>
+        <v>-0.3136246147892646</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7377928047779341</v>
+        <v>0.7377928047779352</v>
       </c>
     </row>
     <row r="7">
@@ -1451,28 +1451,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4477683802567868</v>
+        <v>0.4477683802567867</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2895653303959365</v>
+        <v>-0.2895653303959368</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01856713373965367</v>
+        <v>-0.01856713373965294</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05727139830862007</v>
+        <v>-0.05727139830862012</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2581389830848947</v>
+        <v>-0.258138983084894</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1034945411945802</v>
+        <v>-0.1034945411945805</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5075417408416003</v>
+        <v>-0.5075417408416023</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6140726115156682</v>
+        <v>-0.6140726115156665</v>
       </c>
     </row>
     <row r="8">
@@ -1482,28 +1482,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.250711820370567</v>
+        <v>0.2507118203705671</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5972800050060074</v>
+        <v>0.597280005006007</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1612008086566507</v>
+        <v>0.1612008086566495</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.008070749633974306</v>
+        <v>-0.008070749633973657</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4440285729599784</v>
+        <v>-0.4440285729599806</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5927711598956693</v>
+        <v>0.5927711598956682</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05000455819207979</v>
+        <v>0.05000455819207951</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05753141390902346</v>
+        <v>-0.05753141390902255</v>
       </c>
     </row>
     <row r="9">
@@ -1513,28 +1513,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2415932316530863</v>
+        <v>0.2415932316530864</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5379719566664243</v>
+        <v>0.5379719566664252</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2344502170904465</v>
+        <v>0.2344502170904456</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3528113221942813</v>
+        <v>-0.3528113221942816</v>
       </c>
       <c r="F9" t="n">
         <v>0.5560903906964135</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2700197681337765</v>
+        <v>-0.2700197681337742</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3009189827819044</v>
+        <v>-0.3009189827819041</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008758932085519488</v>
+        <v>0.008758932085519972</v>
       </c>
     </row>
   </sheetData>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.474019129159479</v>
+        <v>0.4740191291594792</v>
       </c>
       <c r="C2" t="n">
-        <v>0.474019129159479</v>
+        <v>0.4740191291594792</v>
       </c>
     </row>
     <row r="3">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2027405400063592</v>
+        <v>0.2027405400063591</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6767596691658382</v>
+        <v>0.6767596691658383</v>
       </c>
     </row>
     <row r="4">
@@ -1599,7 +1599,7 @@
         <v>0.1184451919124842</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7952048610783223</v>
+        <v>0.7952048610783224</v>
       </c>
     </row>
     <row r="5">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09707055577179888</v>
+        <v>0.09707055577179886</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8922754168501212</v>
+        <v>0.8922754168501214</v>
       </c>
     </row>
     <row r="6">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05462411560306306</v>
+        <v>0.05462411560306308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9468995324531843</v>
+        <v>0.9468995324531845</v>
       </c>
     </row>
     <row r="7">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02545633643537516</v>
+        <v>0.02545633643537511</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9723558688885594</v>
+        <v>0.9723558688885596</v>
       </c>
     </row>
     <row r="8">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01451705818638534</v>
+        <v>0.01451705818638529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9868729270749448</v>
+        <v>0.9868729270749449</v>
       </c>
     </row>
     <row r="9">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01312707292505513</v>
+        <v>0.01312707292505505</v>
       </c>
       <c r="C9" t="n">
         <v>0.9999999999999999</v>
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2657309991848752</v>
+        <v>0.2657309991848753</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08512632074477063</v>
+        <v>0.08512632074477056</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4659507318407849</v>
+        <v>0.4659507318407846</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6450632731478942</v>
+        <v>0.6450632731478928</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5349177360509999</v>
+        <v>-0.5349177360510007</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.03758342674437627</v>
+        <v>-0.037583426744376</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03500693295679597</v>
+        <v>-0.03500693295679631</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01220045321332267</v>
+        <v>-0.01220045321332329</v>
       </c>
     </row>
     <row r="3">
@@ -1764,25 +1764,25 @@
         <v>0.479949868894065</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04826009627448326</v>
+        <v>0.04826009627448347</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1486898888421056</v>
+        <v>-0.1486898888421047</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.07814119715424821</v>
+        <v>-0.07814119715424857</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007260623779872549</v>
+        <v>0.007260623779873648</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2591398262463888</v>
+        <v>-0.2591398262464031</v>
       </c>
       <c r="H3" t="n">
-        <v>0.672286853151285</v>
+        <v>0.6722868531512856</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4689654332622309</v>
+        <v>-0.4689654332622225</v>
       </c>
     </row>
     <row r="4">
@@ -1792,28 +1792,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2604292356410101</v>
+        <v>0.2604292356410102</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4355608794495723</v>
+        <v>-0.4355608794495731</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2334617527546636</v>
+        <v>0.2334617527546627</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3632403838213337</v>
+        <v>0.3632403838213352</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7016938307892107</v>
+        <v>0.7016938307892103</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1575841538600077</v>
+        <v>0.1575841538600109</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1177869630415379</v>
+        <v>-0.117786963041533</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1579069368350973</v>
+        <v>-0.1579069368350985</v>
       </c>
     </row>
     <row r="5">
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4150947990759204</v>
+        <v>0.4150947990759205</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.06385126387340842</v>
+        <v>-0.06385126387340835</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4751892896274743</v>
+        <v>-0.4751892896274745</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01522261449202836</v>
+        <v>0.01522261449202792</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2394519370362756</v>
+        <v>-0.2394519370362766</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7189508390154717</v>
+        <v>0.7189508390154746</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1462656219417104</v>
+        <v>-0.1462656219416945</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04428954368451163</v>
+        <v>-0.04428954368451424</v>
       </c>
     </row>
     <row r="6">
@@ -1854,28 +1854,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4400086900240846</v>
+        <v>0.4400086900240844</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03330732986843283</v>
+        <v>0.03330732986843318</v>
       </c>
       <c r="D6" t="n">
         <v>0.1682906455238775</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4304004515180491</v>
+        <v>-0.430400451518049</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07862799138475504</v>
+        <v>-0.07862799138475424</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.305041570672082</v>
+        <v>-0.3050415706720692</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6426767444388718</v>
+        <v>-0.6426767444388752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2818697673265117</v>
+        <v>-0.2818697673265194</v>
       </c>
     </row>
     <row r="7">
@@ -1885,28 +1885,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.471165177948317</v>
+        <v>0.4711651779483171</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2077318446946209</v>
+        <v>-0.2077318446946207</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05359905146542951</v>
+        <v>0.05359905146542967</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1775492517406804</v>
+        <v>-0.1775492517406805</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01570729889702216</v>
+        <v>0.01570729889702218</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1624818936050386</v>
+        <v>-0.1624818936050414</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1675153104550675</v>
+        <v>0.1675153104550541</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8035830986600291</v>
+        <v>0.8035830986600314</v>
       </c>
     </row>
     <row r="8">
@@ -1916,28 +1916,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1272033749144373</v>
+        <v>0.1272033749144372</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6482452511645256</v>
+        <v>0.6482452511645248</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4822998180918568</v>
+        <v>0.4822998180918573</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2373636770591202</v>
+        <v>-0.2373636770591196</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2593324620230434</v>
+        <v>0.2593324620230432</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4275098353982365</v>
+        <v>0.4275098353982345</v>
       </c>
       <c r="H8" t="n">
-        <v>0.145213638330307</v>
+        <v>0.1452136383303145</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05947924054884673</v>
+        <v>0.05947924054884823</v>
       </c>
     </row>
     <row r="9">
@@ -1950,25 +1950,25 @@
         <v>0.1646909518672338</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5763249134284973</v>
+        <v>0.576324913428498</v>
       </c>
       <c r="D9" t="n">
         <v>-0.4654720907390053</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4153338679481142</v>
+        <v>0.4153338679481153</v>
       </c>
       <c r="F9" t="n">
         <v>0.3006932499334872</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2957965129417832</v>
+        <v>-0.2957965129417782</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2221614797030018</v>
+        <v>-0.2221614797030092</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1558597598006236</v>
+        <v>0.1558597598006213</v>
       </c>
     </row>
   </sheetData>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4824013165743099</v>
+        <v>0.4824013165743098</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4824013165743099</v>
+        <v>0.4824013165743098</v>
       </c>
     </row>
     <row r="3">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1786902661212104</v>
+        <v>0.1786902661212103</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6610915826955203</v>
+        <v>0.66109158269552</v>
       </c>
     </row>
     <row r="4">
@@ -2033,7 +2033,7 @@
         <v>0.1180564740041677</v>
       </c>
       <c r="C4" t="n">
-        <v>0.779148056699688</v>
+        <v>0.7791480566996878</v>
       </c>
     </row>
     <row r="5">
@@ -2046,7 +2046,7 @@
         <v>0.1010514169410372</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8801994736407251</v>
+        <v>0.880199473640725</v>
       </c>
     </row>
     <row r="6">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0765891353208345</v>
+        <v>0.07658913532083457</v>
       </c>
       <c r="C6" t="n">
         <v>0.9567886089615596</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0188237879850916</v>
+        <v>0.01882378798509168</v>
       </c>
       <c r="C7" t="n">
         <v>0.9756123969466513</v>
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01552754104524585</v>
+        <v>0.01552754104524577</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9911399379918971</v>
+        <v>0.991139937991897</v>
       </c>
     </row>
     <row r="9">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008860062008103034</v>
+        <v>0.008860062008102992</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -2164,28 +2164,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2667234383307902</v>
+        <v>0.26672343833079</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1049497514679921</v>
+        <v>0.1049497514679926</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3019872800608371</v>
+        <v>-0.3019872800608355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7609999519020298</v>
+        <v>0.76099995190203</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4961579021239469</v>
+        <v>-0.4961579021239481</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.01891687176777775</v>
+        <v>-0.01891687176777806</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02954577909073014</v>
+        <v>-0.0295457790907297</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0111107181937135</v>
+        <v>-0.01111071819371289</v>
       </c>
     </row>
     <row r="3">
@@ -2198,25 +2198,25 @@
         <v>0.4809131832013091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05992975670667532</v>
+        <v>0.05992975670667484</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1230294908187296</v>
+        <v>0.1230294908187292</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1080737426780882</v>
+        <v>-0.108073742678088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008216678999212667</v>
+        <v>0.008216678999213493</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2538455419757857</v>
+        <v>-0.2538455419757767</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6993626477359718</v>
+        <v>0.6993626477359703</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4297691926763377</v>
+        <v>-0.429769192676346</v>
       </c>
     </row>
     <row r="4">
@@ -2226,28 +2226,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2630786052558971</v>
+        <v>0.2630786052558973</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4168087262075644</v>
+        <v>-0.4168087262075632</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1350157694499914</v>
+        <v>-0.1350157694499962</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3841384101415522</v>
+        <v>0.3841384101415521</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7287938045084414</v>
+        <v>0.7287938045084411</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1541905404255236</v>
+        <v>0.1541905404255217</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1102595744290427</v>
+        <v>-0.1102595744290472</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1555514418695947</v>
+        <v>-0.1555514418695939</v>
       </c>
     </row>
     <row r="5">
@@ -2257,28 +2257,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4140058855175091</v>
+        <v>0.4140058855175095</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.06804540094767826</v>
+        <v>-0.06804540094767841</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4896028284187772</v>
+        <v>0.4896028284187787</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08560217293663117</v>
+        <v>-0.08560217293663108</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2372463819589914</v>
+        <v>-0.2372463819589895</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7019047523606515</v>
+        <v>0.7019047523606485</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1566597457261331</v>
+        <v>-0.1566597457261448</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05858229672449757</v>
+        <v>-0.05858229672449863</v>
       </c>
     </row>
     <row r="6">
@@ -2288,28 +2288,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4438308760514366</v>
+        <v>0.4438308760514368</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02565376660875135</v>
+        <v>0.02565376660875066</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2562686468557359</v>
+        <v>-0.2562686468557348</v>
       </c>
       <c r="E6" t="n">
         <v>-0.3607055359290721</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.09650525308232216</v>
+        <v>-0.09650525308232369</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3234520520612941</v>
+        <v>-0.3234520520613063</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6275279425370397</v>
+        <v>-0.6275279425370389</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3144012121336898</v>
+        <v>-0.31440121213368</v>
       </c>
     </row>
     <row r="7">
@@ -2319,28 +2319,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4701535152323121</v>
+        <v>0.4701535152323122</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2161794411450359</v>
+        <v>-0.2161794411450356</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09139408709447526</v>
+        <v>-0.09139408709447523</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.158865538025547</v>
+        <v>-0.1588655380255468</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.00075668862009699</v>
+        <v>-0.0007566886200971307</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1579864965702404</v>
+        <v>-0.1579864965702344</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1276596115261923</v>
+        <v>0.1276596115262057</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8107858539230417</v>
+        <v>0.810785853923041</v>
       </c>
     </row>
     <row r="8">
@@ -2350,28 +2350,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.131908187656173</v>
+        <v>0.1319081876561732</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6396696430774773</v>
+        <v>0.6396696430774791</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5189343824668934</v>
+        <v>-0.5189343824668935</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1622079912571806</v>
+        <v>-0.1622079912571815</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2474907949674714</v>
+        <v>0.2474907949674685</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4433104934745534</v>
+        <v>0.4433104934745552</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1224091220504414</v>
+        <v>0.1224091220504345</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07112504229149993</v>
+        <v>0.07112504229149638</v>
       </c>
     </row>
     <row r="9">
@@ -2384,25 +2384,25 @@
         <v>0.1467649395769892</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5920011522836073</v>
+        <v>0.5920011522836063</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5407474897316703</v>
+        <v>0.5407474897316701</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2695383348271462</v>
+        <v>0.2695383348271471</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3094641127172682</v>
+        <v>0.3094641127172704</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3043919051691511</v>
+        <v>-0.3043919051691543</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2196524435658613</v>
+        <v>-0.2196524435658541</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1620686942518654</v>
+        <v>0.1620686942518693</v>
       </c>
     </row>
   </sheetData>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4794226640017988</v>
+        <v>0.4794226640017987</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4794226640017988</v>
+        <v>0.4794226640017987</v>
       </c>
     </row>
     <row r="3">
@@ -2454,7 +2454,7 @@
         <v>0.1830324404940615</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6624551044958603</v>
+        <v>0.6624551044958602</v>
       </c>
     </row>
     <row r="4">
@@ -2467,7 +2467,7 @@
         <v>0.1119645930688711</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7744196975647314</v>
+        <v>0.7744196975647313</v>
       </c>
     </row>
     <row r="5">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1021654910603933</v>
+        <v>0.1021654910603932</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8765851886251247</v>
+        <v>0.8765851886251245</v>
       </c>
     </row>
     <row r="6">
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07912601862916521</v>
+        <v>0.07912601862916525</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9557112072542899</v>
+        <v>0.9557112072542897</v>
       </c>
     </row>
     <row r="7">
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01933345605901831</v>
+        <v>0.01933345605901839</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9750446633133082</v>
+        <v>0.9750446633133081</v>
       </c>
     </row>
     <row r="8">
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01548754947829141</v>
+        <v>0.01548754947829135</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9905322127915996</v>
+        <v>0.9905322127915994</v>
       </c>
     </row>
     <row r="9">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009467787208400438</v>
+        <v>0.009467787208400257</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9999999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -2714,28 +2714,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06383057955987598</v>
+        <v>0.0638305795598762</v>
       </c>
       <c r="C2" t="n">
-        <v>0.411272485239268</v>
+        <v>0.4112724852392631</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8121857154249568</v>
+        <v>0.8121857154249587</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4070567436599584</v>
+        <v>-0.4070567436599606</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.03557544597759454</v>
+        <v>-0.03557544597759466</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01313306889930471</v>
+        <v>0.01313306889930445</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002224116785078825</v>
+        <v>0.0002224116785090298</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001277410112312377</v>
+        <v>0.00127741011231281</v>
       </c>
     </row>
     <row r="3">
@@ -2745,28 +2745,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1504467751503143</v>
+        <v>0.150446775150315</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6677626436637781</v>
+        <v>0.6677626436637787</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01592975875767411</v>
+        <v>0.01592975875768062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7261827853412152</v>
+        <v>0.7261827853412158</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0252801587900036</v>
+        <v>0.02528015879000337</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.05262410226106758</v>
+        <v>-0.05262410226106506</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01589942783257858</v>
+        <v>-0.01589942783258445</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01422850172696898</v>
+        <v>0.0142285017269657</v>
       </c>
     </row>
     <row r="4">
@@ -2776,28 +2776,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.442630639980426</v>
+        <v>0.4426306399804262</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.08810800469983325</v>
+        <v>-0.08810800469983278</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01939990665689644</v>
+        <v>-0.01939990665689714</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04439553166127466</v>
+        <v>-0.04439553166127296</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.282212171151174</v>
+        <v>-0.2822121711511801</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4049897814116965</v>
+        <v>-0.4049897814117158</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.003671538702831954</v>
+        <v>-0.00367153870291384</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7418179450905387</v>
+        <v>0.7418179450905255</v>
       </c>
     </row>
     <row r="5">
@@ -2807,28 +2807,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4430296992456036</v>
+        <v>0.4430296992456039</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.07326564850094028</v>
+        <v>-0.07326564850094072</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.009990188044397774</v>
+        <v>-0.009990188044398295</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01028898551684256</v>
+        <v>0.01028898551684228</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1920174257733384</v>
+        <v>-0.1920174257733357</v>
       </c>
       <c r="G5" t="n">
-        <v>0.572384473015695</v>
+        <v>0.5723844730157713</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6575130525021865</v>
+        <v>-0.6575130525021194</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03651126257938714</v>
+        <v>-0.03651126257940386</v>
       </c>
     </row>
     <row r="6">
@@ -2838,28 +2838,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4290207180938385</v>
+        <v>0.4290207180938384</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0565663977882894</v>
+        <v>-0.05656639778828935</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002381433008760883</v>
+        <v>-0.002381433008761333</v>
       </c>
       <c r="E6" t="n">
         <v>-0.07529294845828445</v>
       </c>
       <c r="F6" t="n">
-        <v>0.893271953686758</v>
+        <v>0.8932719536867586</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.08241099979150313</v>
+        <v>-0.08241099979150004</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.03989469004127898</v>
+        <v>-0.03989469004128716</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02736465518336589</v>
+        <v>0.02736465518336884</v>
       </c>
     </row>
     <row r="7">
@@ -2869,28 +2869,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4438735363343999</v>
+        <v>0.4438735363344002</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.07097271053936823</v>
+        <v>-0.07097271053936891</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002095076299099259</v>
+        <v>0.00209507629909868</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02905634861806075</v>
+        <v>0.02905634861805937</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.137274908158207</v>
+        <v>-0.1372749081582083</v>
       </c>
       <c r="G7" t="n">
-        <v>0.458455306390668</v>
+        <v>0.4584553063905838</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7504703204166673</v>
+        <v>0.7504703204167228</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0697074398258539</v>
+        <v>-0.06970743982580829</v>
       </c>
     </row>
     <row r="8">
@@ -2900,28 +2900,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4426705667319708</v>
+        <v>0.4426705667319706</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.08471082235640434</v>
+        <v>-0.0847108223564044</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.009106551032648218</v>
+        <v>-0.009106551032649037</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03173696824729836</v>
+        <v>-0.0317369682472988</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2519438370111767</v>
+        <v>-0.2519438370111717</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5361807144925552</v>
+        <v>-0.5361807144925319</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.04889868892444343</v>
+        <v>-0.04889868892447536</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6651467087188102</v>
+        <v>-0.6651467087188292</v>
       </c>
     </row>
     <row r="9">
@@ -2931,28 +2931,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06367498436769611</v>
+        <v>0.06367498436769614</v>
       </c>
       <c r="C9" t="n">
-        <v>0.596996074062034</v>
+        <v>0.5969960740620384</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5826932781236887</v>
+        <v>-0.5826932781236862</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5453127622057695</v>
+        <v>-0.545312762205768</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.03641454664625449</v>
+        <v>-0.03641454664625424</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03090176252272191</v>
+        <v>0.03090176252272012</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01489612104334797</v>
+        <v>0.01489612104335173</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01186955638069084</v>
+        <v>-0.01186955638068884</v>
       </c>
     </row>
   </sheetData>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6166614620539317</v>
+        <v>0.6166614620539318</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6166614620539317</v>
+        <v>0.6166614620539318</v>
       </c>
     </row>
     <row r="3">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1644610527687256</v>
+        <v>0.1644610527687258</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7811225148226573</v>
+        <v>0.7811225148226576</v>
       </c>
     </row>
     <row r="4">
@@ -3017,7 +3017,7 @@
         <v>0.1255538000246208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9066763148472781</v>
+        <v>0.9066763148472784</v>
       </c>
     </row>
     <row r="5">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07140353679666489</v>
+        <v>0.07140353679666497</v>
       </c>
       <c r="C5" t="n">
-        <v>0.978079851643943</v>
+        <v>0.9780798516439434</v>
       </c>
     </row>
     <row r="6">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01319649939274066</v>
+        <v>0.0131964993927404</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9912763510366837</v>
+        <v>0.9912763510366838</v>
       </c>
     </row>
     <row r="7">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004592016562856247</v>
+        <v>0.004592016562856207</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9958683675995399</v>
+        <v>0.99586836759954</v>
       </c>
     </row>
     <row r="8">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002471420042267551</v>
+        <v>0.002471420042267508</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9983397876418074</v>
+        <v>0.9983397876418075</v>
       </c>
     </row>
     <row r="9">
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001660212358192441</v>
+        <v>0.001660212358192374</v>
       </c>
       <c r="C9" t="n">
         <v>0.9999999999999999</v>
@@ -3148,28 +3148,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05963920927971845</v>
+        <v>0.05963920927971825</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4549743241388542</v>
+        <v>0.4549743241388529</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7763197546766787</v>
+        <v>0.7763197546766786</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.430360799869622</v>
+        <v>-0.4303607998696238</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.03586777904293505</v>
+        <v>-0.03586777904293518</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01645737427743842</v>
+        <v>0.01645737427743875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001345476941208789</v>
+        <v>0.000134547694122318</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001178422903926707</v>
+        <v>0.001178422903927515</v>
       </c>
     </row>
     <row r="3">
@@ -3179,28 +3179,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.140595616278948</v>
+        <v>0.1405956162789474</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6725598801813232</v>
+        <v>0.6725598801813215</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.001499240246044969</v>
+        <v>-0.001499240246039649</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7227750987775388</v>
+        <v>0.7227750987775402</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03045244375068434</v>
+        <v>0.03045244375068432</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.06570012909746507</v>
+        <v>-0.06570012909746493</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01279080315356175</v>
+        <v>-0.01279080315356859</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009084392126381362</v>
+        <v>0.009084392126378819</v>
       </c>
     </row>
     <row r="4">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4433342275582587</v>
+        <v>0.4433342275582588</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.08386225110158554</v>
+        <v>-0.08386225110158557</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01454879435839695</v>
+        <v>-0.01454879435839733</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04228775559959681</v>
+        <v>-0.04228775559959707</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2924099067926696</v>
+        <v>-0.2924099067926601</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.397562821682267</v>
+        <v>-0.397562821682271</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.05265284958418881</v>
+        <v>-0.05265284958429093</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7403309330838224</v>
+        <v>0.7403309330838166</v>
       </c>
     </row>
     <row r="5">
@@ -3241,28 +3241,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4439347772012114</v>
+        <v>0.4439347772012117</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.06963314766611869</v>
+        <v>-0.06963314766611892</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00157376352934886</v>
+        <v>0.001573763529348983</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0252641692962757</v>
+        <v>0.02526416929627611</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.163200588841714</v>
+        <v>-0.1632005888417187</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5585796890706257</v>
+        <v>0.5585796890706852</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6720400588695358</v>
+        <v>-0.6720400588694779</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08455082134227705</v>
+        <v>-0.08455082134233131</v>
       </c>
     </row>
     <row r="6">
@@ -3272,28 +3272,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4290968747267123</v>
+        <v>0.4290968747267124</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.06435205255763148</v>
+        <v>-0.06435205255763118</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007534690507843019</v>
+        <v>0.007534690507842254</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07404595360794468</v>
+        <v>-0.07404595360794533</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8866311310729607</v>
+        <v>0.8866311310729597</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1354132361233592</v>
+        <v>-0.1354132361233588</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.04129187671889224</v>
+        <v>-0.04129187671891167</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006211637186940532</v>
+        <v>0.006211637186920993</v>
       </c>
     </row>
     <row r="7">
@@ -3306,25 +3306,25 @@
         <v>0.4445077424755725</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.06662032661985237</v>
+        <v>-0.06662032661985201</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01032523370606623</v>
+        <v>0.01032523370606606</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03780516992076902</v>
+        <v>0.03780516992076908</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1074475733016374</v>
+        <v>-0.1074475733016297</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4920747737628725</v>
+        <v>0.4920747737628093</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7367144351743847</v>
+        <v>0.7367144351744276</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002834547583959895</v>
+        <v>0.00283454758403778</v>
       </c>
     </row>
     <row r="8">
@@ -3334,28 +3334,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4428819535116973</v>
+        <v>0.4428819535116971</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.08292952709461821</v>
+        <v>-0.08292952709461812</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.006191789209719832</v>
+        <v>-0.006191789209720406</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03427202404883214</v>
+        <v>-0.0342720240488328</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2954710028728842</v>
+        <v>-0.2954710028728963</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5128984046524009</v>
+        <v>-0.5128984046523941</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02917952919355491</v>
+        <v>0.02917952919357655</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.666742849189896</v>
+        <v>-0.6667428491898953</v>
       </c>
     </row>
     <row r="9">
@@ -3365,28 +3365,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07209041475096864</v>
+        <v>0.07209041475096874</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5597527654953629</v>
+        <v>0.5597527654953663</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6300075605599867</v>
+        <v>-0.6300075605599866</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5309167545368715</v>
+        <v>-0.5309167545368673</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02617839132799538</v>
+        <v>-0.02617839132799562</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04249800767217388</v>
+        <v>0.04249800767217339</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01102682890328484</v>
+        <v>0.01102682890328929</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.00920365287961754</v>
+        <v>-0.009203652879615266</v>
       </c>
     </row>
   </sheetData>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6152841912169235</v>
+        <v>0.6152841912169233</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6152841912169235</v>
+        <v>0.6152841912169233</v>
       </c>
     </row>
     <row r="3">
@@ -3438,7 +3438,7 @@
         <v>0.1657302009803309</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7810143921972544</v>
+        <v>0.7810143921972543</v>
       </c>
     </row>
     <row r="4">
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1245643732519409</v>
+        <v>0.1245643732519408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9055787654491954</v>
+        <v>0.9055787654491951</v>
       </c>
     </row>
     <row r="5">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07243179736027842</v>
+        <v>0.0724317973602782</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9780105628094737</v>
+        <v>0.9780105628094733</v>
       </c>
     </row>
     <row r="6">
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01339793029378336</v>
+        <v>0.01339793029378354</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9914084931032571</v>
+        <v>0.9914084931032568</v>
       </c>
     </row>
     <row r="7">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004599302282579838</v>
+        <v>0.004599302282580033</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9960077953858369</v>
+        <v>0.9960077953858368</v>
       </c>
     </row>
     <row r="8">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002408204258875786</v>
+        <v>0.002408204258875709</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9984159996447127</v>
+        <v>0.9984159996447125</v>
       </c>
     </row>
     <row r="9">
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001584000355287383</v>
+        <v>0.001584000355287318</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -3582,28 +3582,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2412261999085927</v>
+        <v>0.2412261999085928</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1800204657611049</v>
+        <v>0.1800204657611047</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8392414741372679</v>
+        <v>0.8392414741372675</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2710950487281043</v>
+        <v>-0.2710950487281027</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3385291054480853</v>
+        <v>0.338529105448087</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08970201130498372</v>
+        <v>0.0897020113049867</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0945228041704676</v>
+        <v>-0.09452280417046534</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0008991395539426244</v>
+        <v>-0.0008991395539423531</v>
       </c>
     </row>
     <row r="3">
@@ -3613,28 +3613,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4319113590619811</v>
+        <v>0.4319113590619809</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2403001709098072</v>
+        <v>0.2403001709098073</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1410482197228412</v>
+        <v>-0.1410482197228406</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1113606535686833</v>
+        <v>-0.1113606535686842</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1239086001767209</v>
+        <v>-0.1239086001767198</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4943373163730325</v>
+        <v>0.4943373163730111</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6541239246322401</v>
+        <v>0.6541239246322577</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1892400010325306</v>
+        <v>-0.1892400010325273</v>
       </c>
     </row>
     <row r="4">
@@ -3644,28 +3644,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.31188377427024</v>
+        <v>0.3118837742702401</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3026845728234188</v>
+        <v>-0.3026845728234192</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3133158237629055</v>
+        <v>0.3133158237629051</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7406826536281631</v>
+        <v>0.7406826536281611</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3213364335893216</v>
+        <v>-0.3213364335893245</v>
       </c>
       <c r="G4" t="n">
-        <v>0.157467830945323</v>
+        <v>0.1574678309453296</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1230227298961385</v>
+        <v>-0.1230227298961333</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1454137150001399</v>
+        <v>-0.1454137150001376</v>
       </c>
     </row>
     <row r="5">
@@ -3681,22 +3681,22 @@
         <v>-0.3313436344559025</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3347214455233264</v>
+        <v>-0.3347214455233274</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1135241983392134</v>
+        <v>-0.1135241983392123</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3985507157907028</v>
+        <v>0.398550715790704</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4774447691550257</v>
+        <v>0.4774447691550388</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4431574346218788</v>
+        <v>-0.4431574346218616</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2046308096912343</v>
+        <v>0.2046308096912372</v>
       </c>
     </row>
     <row r="6">
@@ -3706,28 +3706,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4451575037370546</v>
+        <v>0.4451575037370545</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1871409932735419</v>
+        <v>-0.1871409932735413</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1295334075162633</v>
+        <v>-0.1295334075162631</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2881040086891544</v>
+        <v>-0.288104008689153</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.05073313920208074</v>
+        <v>-0.05073313920208094</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4586631797584643</v>
+        <v>-0.4586631797584546</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1548808901669419</v>
+        <v>-0.1548808901669579</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6558173282243344</v>
+        <v>-0.6558173282243382</v>
       </c>
     </row>
     <row r="7">
@@ -3737,28 +3737,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4392155181404368</v>
+        <v>0.4392155181404367</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2709009244577495</v>
+        <v>-0.2709009244577498</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03598386951656331</v>
+        <v>0.0359838695165635</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1097629093413543</v>
+        <v>-0.1097629093413554</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1522851184964729</v>
+        <v>-0.1522851184964724</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4264447666587726</v>
+        <v>-0.4264447666587874</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2828819645632407</v>
+        <v>0.2828819645632261</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6597663074292309</v>
+        <v>0.6597663074292277</v>
       </c>
     </row>
     <row r="8">
@@ -3768,28 +3768,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2433432240865523</v>
+        <v>0.2433432240865524</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5959938673411863</v>
+        <v>0.5959938673411864</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07940498445334432</v>
+        <v>-0.07940498445334455</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1115440504304781</v>
+        <v>-0.1115440504304808</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5326337921272374</v>
+        <v>-0.5326337921272366</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04450249886224497</v>
+        <v>0.04450249886226163</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4961481968178777</v>
+        <v>-0.496148196817876</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1870451723887269</v>
+        <v>0.1870451723887283</v>
       </c>
     </row>
     <row r="9">
@@ -3799,28 +3799,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2597553947520085</v>
+        <v>0.2597553947520084</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4947970825544086</v>
+        <v>0.4947970825544085</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2029655197398655</v>
+        <v>-0.2029655197398653</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4950897404727439</v>
+        <v>0.4950897404727467</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5463346609111996</v>
+        <v>0.5463346609111973</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3172176186012434</v>
+        <v>-0.3172176186012452</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03861214270186818</v>
+        <v>0.0386121427018573</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02818956970588078</v>
+        <v>0.02818956970587866</v>
       </c>
     </row>
   </sheetData>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.503018590360603</v>
+        <v>0.5030185903606031</v>
       </c>
       <c r="C2" t="n">
-        <v>0.503018590360603</v>
+        <v>0.5030185903606031</v>
       </c>
     </row>
     <row r="3">
@@ -3872,7 +3872,7 @@
         <v>0.2049820734976533</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7080006638582563</v>
+        <v>0.7080006638582564</v>
       </c>
     </row>
     <row r="4">
@@ -3885,7 +3885,7 @@
         <v>0.1096230647863358</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8176237286445921</v>
+        <v>0.8176237286445922</v>
       </c>
     </row>
     <row r="5">
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07261235036512105</v>
+        <v>0.072612350365121</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8902360790097131</v>
+        <v>0.8902360790097132</v>
       </c>
     </row>
     <row r="6">
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05368203207704346</v>
+        <v>0.05368203207704347</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9439181110867566</v>
+        <v>0.9439181110867567</v>
       </c>
     </row>
     <row r="7">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02482994167404395</v>
+        <v>0.02482994167404389</v>
       </c>
       <c r="C7" t="n">
         <v>0.9687480527608006</v>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02100207815939811</v>
+        <v>0.02100207815939802</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9897501309201987</v>
+        <v>0.9897501309201986</v>
       </c>
     </row>
     <row r="9">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01024986907980121</v>
+        <v>0.01024986907980137</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4016,28 +4016,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2593377431194712</v>
+        <v>0.2593377431194716</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1988900115374296</v>
+        <v>0.19889001153743</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8024693140182633</v>
+        <v>0.8024693140182638</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3317416262655393</v>
+        <v>-0.3317416262655357</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3486053584145886</v>
+        <v>0.3486053584145896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09557283748777783</v>
+        <v>0.09557283748777674</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.09205934735200823</v>
+        <v>-0.09205934735200985</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.00651192370860918</v>
+        <v>-0.006511923708607674</v>
       </c>
     </row>
     <row r="3">
@@ -4047,28 +4047,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4338184750422479</v>
+        <v>0.4338184750422474</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2428468867827041</v>
+        <v>0.2428468867827035</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1505723976033162</v>
+        <v>-0.1505723976033158</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08237297881170418</v>
+        <v>-0.08237297881170584</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1564653588442402</v>
+        <v>-0.1564653588442383</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4733715014653813</v>
+        <v>0.4733715014653866</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6468203393809872</v>
+        <v>0.6468203393809826</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2375521571757697</v>
+        <v>-0.2375521571757718</v>
       </c>
     </row>
     <row r="4">
@@ -4078,28 +4078,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3028135984307666</v>
+        <v>0.3028135984307664</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2915754028598662</v>
+        <v>-0.2915754028598648</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3550243057168505</v>
+        <v>0.3550243057168485</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7557667083230935</v>
+        <v>0.7557667083230922</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2426006395409458</v>
+        <v>-0.2426006395409511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1636530788036056</v>
+        <v>0.1636530788036057</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1445204705455853</v>
+        <v>-0.1445204705455874</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1397804245199238</v>
+        <v>-0.1397804245199227</v>
       </c>
     </row>
     <row r="5">
@@ -4109,28 +4109,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3634164391629133</v>
+        <v>0.3634164391629132</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3535289831750537</v>
+        <v>-0.3535289831750538</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3581199940010002</v>
+        <v>-0.358119994000999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.13798348126235</v>
+        <v>-0.1379834812623484</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3856218493827271</v>
+        <v>0.3856218493827273</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4925837029388673</v>
+        <v>0.4925837029388639</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.406773159129643</v>
+        <v>-0.4067731591296451</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1971016501356012</v>
+        <v>0.1971016501356067</v>
       </c>
     </row>
     <row r="6">
@@ -4143,25 +4143,25 @@
         <v>0.4447914378570711</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2013299664200613</v>
+        <v>-0.2013299664200615</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.137958210428876</v>
+        <v>-0.1379582104288756</v>
       </c>
       <c r="E6" t="n">
         <v>-0.2612562559034199</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0737676717599814</v>
+        <v>-0.07376767175997896</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.486074854310407</v>
+        <v>-0.4860748543104051</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1823279013691639</v>
+        <v>-0.1823279013691649</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.631969639578889</v>
+        <v>-0.6319696395788899</v>
       </c>
     </row>
     <row r="7">
@@ -4171,28 +4171,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4401529390358664</v>
+        <v>0.4401529390358667</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2768538137430856</v>
+        <v>-0.2768538137430852</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04743410658641052</v>
+        <v>0.04743410658641063</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08888690745756617</v>
+        <v>-0.08888690745756656</v>
       </c>
       <c r="F7" t="n">
         <v>-0.160111391446756</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4006985315907139</v>
+        <v>-0.400698531590715</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3064181495252987</v>
+        <v>0.3064181495253059</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6628570177953149</v>
+        <v>0.6628570177953106</v>
       </c>
     </row>
     <row r="8">
@@ -4202,28 +4202,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2527309992205826</v>
+        <v>0.2527309992205825</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5800226902625417</v>
+        <v>0.5800226902625418</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08959264976901811</v>
+        <v>-0.08959264976901971</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.07538239020301206</v>
+        <v>-0.07538239020301586</v>
       </c>
       <c r="F8" t="n">
         <v>-0.5295766538075403</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0542380463907409</v>
+        <v>0.0542380463907366</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5082052303916308</v>
+        <v>-0.5082052303916287</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2105365028600292</v>
+        <v>0.2105365028600319</v>
       </c>
     </row>
     <row r="9">
@@ -4233,28 +4233,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2555990828570615</v>
+        <v>0.2555990828570613</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4877100415315639</v>
+        <v>0.4877100415315636</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2230906994946595</v>
+        <v>-0.2230906994946602</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4594575159193925</v>
+        <v>0.4594575159193957</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5787096467257593</v>
+        <v>0.5787096467257564</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3124009872646986</v>
+        <v>-0.3124009872646979</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03728073979359869</v>
+        <v>0.03728073979360081</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04525781124961127</v>
+        <v>0.04525781124961006</v>
       </c>
     </row>
   </sheetData>
